--- a/tests/fixtures/qualification_workbook.xlsx
+++ b/tests/fixtures/qualification_workbook.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="94">
   <si>
     <t xml:space="preserve">Synthetic formula-qualification inputs</t>
   </si>
@@ -213,6 +213,39 @@
   </si>
   <si>
     <t xml:space="preserve">Function outside the catalogue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and_all_true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and_one_false</t>
+  </si>
+  <si>
+    <t xml:space="preserve">or_one_true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">or_all_false</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sumproduct_2d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">npv_cash_flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excel convention: first flow at period 1, not 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choose_index_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choose_index_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xlookup_exact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XLOOKUP not in Excel/LibreOffice; VLOOKUP-equivalent formula used for fixture</t>
   </si>
   <si>
     <t xml:space="preserve">Cross-tab range inputs</t>
@@ -865,7 +898,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -1430,6 +1463,154 @@
       </c>
       <c r="E35" s="2" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36" s="6" t="n">
+        <f aca="false">IF(AND(TRUE(),TRUE(),TRUE()),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" s="6" t="n">
+        <f aca="false">IF(AND(TRUE(),FALSE(),TRUE()),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" s="6" t="n">
+        <f aca="false">IF(OR(FALSE(),TRUE(),FALSE()),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" s="6" t="n">
+        <f aca="false">IF(OR(FALSE(),FALSE(),FALSE()),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B40" s="6" t="n">
+        <f aca="false">SUMPRODUCT(Inputs!$B$4:$B$6,Inputs!$F$4:$F$6)</f>
+        <v>28.5</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B41" s="6" t="n">
+        <f aca="false">NPV(0.1,-1000,300,300,300)</f>
+        <v>-230.858547913394</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>-230.858</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" s="6" t="n">
+        <f aca="false">CHOOSE(1,10,20,30)</f>
+        <v>10</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" s="6" t="n">
+        <f aca="false">CHOOSE(2,10,20,30)</f>
+        <v>20</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B44" s="6" t="n">
+        <f aca="false">VLOOKUP("Property",Inputs!$E$4:$F$6,2,FALSE())</f>
+        <v>1.2</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1460,13 +1641,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>3</v>
@@ -1474,7 +1655,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>4</v>
@@ -1482,7 +1663,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>6</v>
@@ -1490,7 +1671,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>10</v>
@@ -1524,22 +1705,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1600,48 +1781,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="B1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/qualification_workbook.xlsx
+++ b/tests/fixtures/qualification_workbook.xlsx
@@ -245,7 +245,7 @@
     <t xml:space="preserve">xlookup_exact</t>
   </si>
   <si>
-    <t xml:space="preserve">XLOOKUP not in Excel/LibreOffice; VLOOKUP-equivalent formula used for fixture</t>
+    <t xml:space="preserve">Exact numeric XLOOKUP, recalculated through LibreOffice</t>
   </si>
   <si>
     <t xml:space="preserve">Cross-tab range inputs</t>
@@ -1554,7 +1554,7 @@
         <v>-230.858547913394</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>-230.858</v>
+        <v>-230.8585</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>22</v>
@@ -1600,7 +1600,7 @@
         <v>72</v>
       </c>
       <c r="B44" s="6" t="n">
-        <f aca="false">VLOOKUP("Property",Inputs!$E$4:$F$6,2,FALSE())</f>
+        <f aca="false">_xlfn.XLOOKUP("Property",Inputs!$E$4:$E$6,Inputs!$F$4:$F$6,,0,1)</f>
         <v>1.2</v>
       </c>
       <c r="C44" s="6" t="n">

--- a/tests/fixtures/qualification_workbook.xlsx
+++ b/tests/fixtures/qualification_workbook.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="102">
   <si>
     <t xml:space="preserve">Synthetic formula-qualification inputs</t>
   </si>
@@ -246,6 +246,30 @@
   </si>
   <si>
     <t xml:space="preserve">Exact numeric XLOOKUP, recalculated through LibreOffice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date_leap_day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leap-day construction as an Excel serial date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">edate_month_end_clamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">January month-end clamps to the 2024 leap day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">networkdays_inclusive_week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inclusive Monday-to-Sunday working-day count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yearfrac_actual_365_leap_year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual/365 basis across the 2024 leap year</t>
   </si>
   <si>
     <t xml:space="preserve">Cross-tab range inputs</t>
@@ -898,7 +922,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -1611,6 +1635,78 @@
       </c>
       <c r="E44" s="2" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" s="6" t="n">
+        <f aca="false">DATE(2024,2,29)</f>
+        <v>45351</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B46" s="6" t="n">
+        <f aca="false">EDATE(DATE(2024,1,31),1)</f>
+        <v>45351</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" s="6" t="n">
+        <f aca="false">NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,7))</f>
+        <v>5</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B48" s="6" t="n">
+        <f aca="false">YEARFRAC(DATE(2024,1,1),DATE(2025,1,1),3)</f>
+        <v>1.0027397260274</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>1.0027397260274</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1641,13 +1737,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>3</v>
@@ -1655,7 +1751,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>4</v>
@@ -1663,7 +1759,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>6</v>
@@ -1671,7 +1767,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>10</v>
@@ -1705,22 +1801,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1781,48 +1877,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/qualification_workbook.xlsx
+++ b/tests/fixtures/qualification_workbook.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="105">
   <si>
     <t xml:space="preserve">Synthetic formula-qualification inputs</t>
   </si>
@@ -96,6 +96,15 @@
   </si>
   <si>
     <t xml:space="preserve">Blank/text ignored; zero retained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_mixed_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blank cell excluded from consideration, not treated as 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">min_mixed_range</t>
   </si>
   <si>
     <t xml:space="preserve">abs_negative</t>
@@ -922,7 +931,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -990,291 +999,295 @@
         <v>24</v>
       </c>
       <c r="B5" s="6" t="n">
+        <f aca="false">MAX(Inputs!$B$4:$B$8)</f>
+        <v>20</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <f aca="false">MIN(Inputs!$B$4:$B$8)</f>
+        <v>-5</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <f aca="false">ABS(Inputs!$B$6)</f>
         <v>5</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C7" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="6" t="n">
-        <f aca="false">INT(-1.2)</f>
-        <v>-2</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="6" t="n">
-        <f aca="false">ROUND(2.5,0)</f>
-        <v>3</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="D7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">ROUND(-2.5,0)</f>
-        <v>-3</v>
+        <f aca="false">INT(-1.2)</f>
+        <v>-2</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="6" t="n">
+        <f aca="false">ROUND(2.5,0)</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <f aca="false">ROUND(-2.5,0)</f>
+        <v>-3</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="6" t="n">
         <f aca="false">ROUNDUP(-1.21,1)</f>
         <v>-1.3</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C11" s="6" t="n">
         <v>-1.3</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="6" t="n">
+      <c r="D11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="6" t="n">
         <f aca="false">ROUNDDOWN(-1.29,1)</f>
         <v>-1.2</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C12" s="6" t="n">
         <v>-1.2</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="6" t="n">
+      <c r="D12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="6" t="n">
         <f aca="false">CEILING(2.1,0.5)</f>
         <v>2.5</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C13" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="6" t="n">
+      <c r="D13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="6" t="n">
         <f aca="false">FLOOR(2.9,0.5)</f>
         <v>2.5</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C14" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="6" t="n">
+      <c r="D14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="6" t="n">
         <f aca="false">SUMIF(Inputs!$A$4:$A$8,"Motor",Inputs!$B$4:$B$8)</f>
         <v>5</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C15" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="6" t="n">
+      <c r="D15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="6" t="n">
         <f aca="false">SUMIFS(Inputs!$B$4:$B$8,Inputs!$A$4:$A$8,"Motor",Inputs!$C$4:$C$8,"North")</f>
         <v>5</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C16" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIF(Inputs!$A$4:$A$8,"Motor")</f>
-        <v>3</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="6" t="n">
-        <f aca="false">COUNTIFS(Inputs!$A$4:$A$8,"Motor",Inputs!$D$4:$D$8,TRUE())</f>
-        <v>3</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="D16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="E16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B17" s="6" t="n">
-        <f aca="false">AVERAGEIF(Inputs!$A$4:$A$8,"Motor",Inputs!$B$4:$B$8)</f>
-        <v>1.66666666666667</v>
+        <f aca="false">COUNTIF(Inputs!$A$4:$A$8,"Motor")</f>
+        <v>3</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>1.66666666666667</v>
+        <v>3</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="E17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <f aca="false">COUNTIFS(Inputs!$A$4:$A$8,"Motor",Inputs!$D$4:$D$8,TRUE())</f>
+        <v>3</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="6" t="n">
-        <f aca="false">AVERAGEIFS(Inputs!$B$4:$B$8,Inputs!$A$4:$A$8,"Motor",Inputs!$C$4:$C$8,"North")</f>
-        <v>2.5</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B19" s="6" t="n">
+        <f aca="false">AVERAGEIF(Inputs!$A$4:$A$8,"Motor",Inputs!$B$4:$B$8)</f>
+        <v>1.66666666666667</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>1.66666666666667</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="6" t="n">
+        <f aca="false">AVERAGEIFS(Inputs!$B$4:$B$8,Inputs!$A$4:$A$8,"Motor",Inputs!$C$4:$C$8,"North")</f>
+        <v>2.5</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="6" t="n">
         <f aca="false">_xlfn.MINIFS(Inputs!$B$4:$B$8,Inputs!$A$4:$A$8,"Motor")</f>
         <v>-5</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C21" s="6" t="n">
         <v>-5</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="6" t="n">
+      <c r="D21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="6" t="n">
         <f aca="false">_xlfn.MAXIFS(Inputs!$B$4:$B$8,Inputs!$A$4:$A$8,"Motor")</f>
         <v>10</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C22" s="6" t="n">
         <v>10</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="6" t="n">
-        <f aca="false">IF(TRUE(),11,22)</f>
-        <v>11</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="6" t="n">
-        <f aca="false">IF(FALSE(),11,22)</f>
-        <v>22</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>22</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>22</v>
@@ -1283,7 +1296,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B23" s="6" t="n">
         <f aca="false">IF(TRUE(),11,22)</f>
@@ -1299,7 +1312,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B24" s="6" t="n">
         <f aca="false">IF(FALSE(),11,22)</f>
@@ -1315,288 +1328,286 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B25" s="6" t="n">
+        <f aca="false">IF(TRUE(),11,22)</f>
+        <v>11</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="6" t="n">
+        <f aca="false">IF(FALSE(),11,22)</f>
+        <v>22</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="6" t="n">
         <f aca="false">VLOOKUP("Property",Inputs!$E$4:$F$6,2,FALSE())</f>
         <v>1.2</v>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C27" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="6" t="n">
+      <c r="D27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="6" t="n">
         <f aca="false">MATCH("Liability",Inputs!$E$4:$E$6,0)</f>
         <v>3</v>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C28" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" s="6" t="n">
+      <c r="D28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="6" t="n">
         <f aca="false">INDEX(Inputs!$F$4:$F$6,2)</f>
         <v>1.2</v>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C29" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="6" t="n">
+      <c r="D29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="6" t="n">
         <f aca="false">INDEX(Inputs!$F$4:$F$6,MATCH("Liability",Inputs!$E$4:$E$6,0))</f>
         <v>1.3</v>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C30" s="6" t="n">
         <v>1.3</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="6" t="n">
+      <c r="D30" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" s="6" t="n">
         <f aca="false">ROUND(SUMIF(Inputs!$A$4:$A$8,"Motor",Inputs!$B$4:$B$8),2)</f>
         <v>5</v>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C31" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="6" t="n">
+      <c r="D31" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" s="6" t="n">
         <f aca="false">SUM('Cross Tab'!$B$3:$B$5)</f>
         <v>20</v>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="C32" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" s="6" t="n">
+      <c r="D32" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="6" t="n">
         <f aca="false">(Inputs!$B$4+Inputs!$B$5)*2/3</f>
         <v>20</v>
       </c>
-      <c r="C31" s="6" t="n">
+      <c r="C33" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="6" t="n">
+      <c r="D33" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="6" t="n">
         <f aca="false">VLOOKUP("Property",Inputs!$E$4:$F$6,2,TRUE())</f>
         <v>1.2</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B33" s="6" t="n">
+      <c r="C34" s="6"/>
+      <c r="D34" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="6" t="n">
         <f aca="false">MATCH("Property",Inputs!$E$4:$E$6,1)</f>
         <v>2</v>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="C35" s="6"/>
+      <c r="D35" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="6" t="e">
+      <c r="E35" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" s="6" t="e">
         <f aca="false">INDEX(Inputs!$B$4:$B$8,0)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35" s="6" t="n">
-        <f aca="true">OFFSET(Inputs!$B$4,1,0)</f>
-        <v>20</v>
-      </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+      <c r="C36" s="6"/>
+      <c r="D36" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B36" s="6" t="n">
-        <f aca="false">IF(AND(TRUE(),TRUE(),TRUE()),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="C36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B37" s="6" t="n">
+        <f aca="true">OFFSET(Inputs!$B$4,1,0)</f>
+        <v>20</v>
+      </c>
+      <c r="C37" s="6"/>
+      <c r="D37" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38" s="6" t="n">
+        <f aca="false">IF(AND(TRUE(),TRUE(),TRUE()),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" s="6" t="n">
         <f aca="false">IF(AND(TRUE(),FALSE(),TRUE()),1,0)</f>
         <v>0</v>
       </c>
-      <c r="C37" s="6" t="n">
+      <c r="C39" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E37" s="2"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B38" s="6" t="n">
+      <c r="D39" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" s="6" t="n">
         <f aca="false">IF(OR(FALSE(),TRUE(),FALSE()),1,0)</f>
         <v>1</v>
       </c>
-      <c r="C38" s="6" t="n">
+      <c r="C40" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B39" s="6" t="n">
+      <c r="D40" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" s="6" t="n">
         <f aca="false">IF(OR(FALSE(),FALSE(),FALSE()),1,0)</f>
         <v>0</v>
       </c>
-      <c r="C39" s="6" t="n">
+      <c r="C41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E39" s="2"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B40" s="6" t="n">
-        <f aca="false">SUMPRODUCT(Inputs!$B$4:$B$6,Inputs!$F$4:$F$6)</f>
-        <v>28.5</v>
-      </c>
-      <c r="C40" s="6" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E40" s="2"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B41" s="6" t="n">
-        <f aca="false">NPV(0.1,-1000,300,300,300)</f>
-        <v>-230.858547913394</v>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>-230.8585</v>
-      </c>
       <c r="D41" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>69</v>
-      </c>
+      <c r="E41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B42" s="6" t="n">
-        <f aca="false">CHOOSE(1,10,20,30)</f>
-        <v>10</v>
+        <f aca="false">SUMPRODUCT(Inputs!$B$4:$B$6,Inputs!$F$4:$F$6)</f>
+        <v>28.5</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>10</v>
+        <v>28.5</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>22</v>
@@ -1608,105 +1619,139 @@
         <v>71</v>
       </c>
       <c r="B43" s="6" t="n">
-        <f aca="false">CHOOSE(2,10,20,30)</f>
-        <v>20</v>
+        <f aca="false">NPV(0.1,-1000,300,300,300)</f>
+        <v>-230.858547913394</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>20</v>
+        <v>-230.8585</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B44" s="6" t="n">
-        <f aca="false">_xlfn.XLOOKUP("Property",Inputs!$E$4:$E$6,Inputs!$F$4:$F$6,,0,1)</f>
-        <v>1.2</v>
+        <f aca="false">CHOOSE(1,10,20,30)</f>
+        <v>10</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>1.2</v>
+        <v>10</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>73</v>
-      </c>
+      <c r="E44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
         <v>74</v>
       </c>
       <c r="B45" s="6" t="n">
+        <f aca="false">CHOOSE(2,10,20,30)</f>
+        <v>20</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B46" s="6" t="n">
+        <f aca="false">_xlfn.XLOOKUP("Property",Inputs!$E$4:$E$6,Inputs!$F$4:$F$6,,0,1)</f>
+        <v>1.2</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B47" s="6" t="n">
         <f aca="false">DATE(2024,2,29)</f>
         <v>45351</v>
       </c>
-      <c r="C45" s="6" t="n">
+      <c r="C47" s="6" t="n">
         <v>45351</v>
       </c>
-      <c r="D45" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B46" s="6" t="n">
+      <c r="D47" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" s="6" t="n">
         <f aca="false">EDATE(DATE(2024,1,31),1)</f>
         <v>45351</v>
       </c>
-      <c r="C46" s="6" t="n">
+      <c r="C48" s="6" t="n">
         <v>45351</v>
       </c>
-      <c r="D46" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B47" s="6" t="n">
+      <c r="D48" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="6" t="n">
         <f aca="false">NETWORKDAYS(DATE(2024,1,1),DATE(2024,1,7))</f>
         <v>5</v>
       </c>
-      <c r="C47" s="6" t="n">
+      <c r="C49" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D47" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B48" s="6" t="n">
+      <c r="D49" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B50" s="6" t="n">
         <f aca="false">YEARFRAC(DATE(2024,1,1),DATE(2025,1,1),3)</f>
         <v>1.0027397260274</v>
       </c>
-      <c r="C48" s="6" t="n">
+      <c r="C50" s="6" t="n">
         <v>1.0027397260274</v>
       </c>
-      <c r="D48" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>81</v>
+      <c r="D50" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1737,13 +1782,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>3</v>
@@ -1751,7 +1796,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>4</v>
@@ -1759,7 +1804,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>6</v>
@@ -1767,7 +1812,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>10</v>
@@ -1801,22 +1846,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1877,48 +1922,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
